--- a/SBM-ressources-corps/ig/mappingAuteurCDAFHIR.xlsx
+++ b/SBM-ressources-corps/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T19:35:04+00:00</t>
+    <t>2025-08-22T19:36:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-ressources-corps/ig/mappingAuteurCDAFHIR.xlsx
+++ b/SBM-ressources-corps/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T19:36:46+00:00</t>
+    <t>2025-08-22T19:39:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
